--- a/public/participants-exemple.xlsx
+++ b/public/participants-exemple.xlsx
@@ -397,306 +397,1446 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:K41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nom</v>
+        <v>Référence commande</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date de la commande</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Statut de la commande</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Nom participant</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Prénom participant</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nom payeur</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Prénom payeur</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Email payeur</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Moyen de paiement</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Tarif</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Montant tarif</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Vincent Auriol</v>
+      <c r="A2">
+        <v>191584750</v>
+      </c>
+      <c r="B2" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="H2" t="str">
+        <v>vincent.auriol@example.com</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J2" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>René Coty</v>
+      <c r="A3">
+        <v>191584751</v>
+      </c>
+      <c r="B3" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="H3" t="str">
+        <v>vincent.auriol@example.com</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J3" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Charles de Gaulle</v>
+      <c r="A4">
+        <v>191584752</v>
+      </c>
+      <c r="B4" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Auriol</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Vincent</v>
+      </c>
+      <c r="H4" t="str">
+        <v>vincent.auriol@example.com</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J4" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Georges Pompidou</v>
+      <c r="A5">
+        <v>191584753</v>
+      </c>
+      <c r="B5" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Coty</v>
+      </c>
+      <c r="E5" t="str">
+        <v>René</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Coty</v>
+      </c>
+      <c r="G5" t="str">
+        <v>René</v>
+      </c>
+      <c r="H5" t="str">
+        <v>ren.coty@example.com</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J5" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Valéry Giscard d’Estaing</v>
+      <c r="A6">
+        <v>191584754</v>
+      </c>
+      <c r="B6" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D6" t="str">
+        <v>de Gaulle</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Charles</v>
+      </c>
+      <c r="F6" t="str">
+        <v>de Gaulle</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Charles</v>
+      </c>
+      <c r="H6" t="str">
+        <v>charles.degaulle@example.com</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J6" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>François Mitterrand</v>
+      <c r="A7">
+        <v>191584755</v>
+      </c>
+      <c r="B7" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D7" t="str">
+        <v>de Gaulle</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Charles</v>
+      </c>
+      <c r="F7" t="str">
+        <v>de Gaulle</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Charles</v>
+      </c>
+      <c r="H7" t="str">
+        <v>charles.degaulle@example.com</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J7" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Jacques Chirac</v>
+      <c r="A8">
+        <v>191584756</v>
+      </c>
+      <c r="B8" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Pompidou</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Georges</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Pompidou</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Georges</v>
+      </c>
+      <c r="H8" t="str">
+        <v>georges.pompidou@example.com</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J8" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Nicolas Sarkozy</v>
+      <c r="A9">
+        <v>191584757</v>
+      </c>
+      <c r="B9" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Giscard d Estaing</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Valéry</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Giscard d Estaing</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Valéry</v>
+      </c>
+      <c r="H9" t="str">
+        <v>valry.giscarddestaing@example.com</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J9" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>François Hollande</v>
+      <c r="A10">
+        <v>191584758</v>
+      </c>
+      <c r="B10" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="E10" t="str">
+        <v>François</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="G10" t="str">
+        <v>François</v>
+      </c>
+      <c r="H10" t="str">
+        <v>franois.mitterrand@example.com</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J10" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Emmanuel Macron</v>
+      <c r="A11">
+        <v>191584759</v>
+      </c>
+      <c r="B11" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="E11" t="str">
+        <v>François</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="G11" t="str">
+        <v>François</v>
+      </c>
+      <c r="H11" t="str">
+        <v>franois.mitterrand@example.com</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J11" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Pierre Mendès France</v>
+      <c r="A12">
+        <v>191584760</v>
+      </c>
+      <c r="B12" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="E12" t="str">
+        <v>François</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="G12" t="str">
+        <v>François</v>
+      </c>
+      <c r="H12" t="str">
+        <v>franois.mitterrand@example.com</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J12" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Guy Mollet</v>
+      <c r="A13">
+        <v>191584761</v>
+      </c>
+      <c r="B13" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="E13" t="str">
+        <v>François</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="G13" t="str">
+        <v>François</v>
+      </c>
+      <c r="H13" t="str">
+        <v>franois.mitterrand@example.com</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J13" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K13">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>Antoine Pinay</v>
+      <c r="A14">
+        <v>191584762</v>
+      </c>
+      <c r="B14" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="E14" t="str">
+        <v>François</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Mitterrand</v>
+      </c>
+      <c r="G14" t="str">
+        <v>François</v>
+      </c>
+      <c r="H14" t="str">
+        <v>franois.mitterrand@example.com</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J14" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K14">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>Edgar Faure</v>
+      <c r="A15">
+        <v>191584763</v>
+      </c>
+      <c r="B15" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Chirac</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Jacques</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Chirac</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Jacques</v>
+      </c>
+      <c r="H15" t="str">
+        <v>jacques.chirac@example.com</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J15" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>Robert Schuman</v>
+      <c r="A16">
+        <v>191584764</v>
+      </c>
+      <c r="B16" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Chirac</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Jacques</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Chirac</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Jacques</v>
+      </c>
+      <c r="H16" t="str">
+        <v>jacques.chirac@example.com</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J16" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K16">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>Georges Bidault</v>
+      <c r="A17">
+        <v>191584765</v>
+      </c>
+      <c r="B17" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Sarkozy</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Nicolas</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Sarkozy</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Nicolas</v>
+      </c>
+      <c r="H17" t="str">
+        <v>nicolas.sarkozy@example.com</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J17" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>Henri Queuille</v>
+      <c r="A18">
+        <v>191584766</v>
+      </c>
+      <c r="B18" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Hollande</v>
+      </c>
+      <c r="E18" t="str">
+        <v>François</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Hollande</v>
+      </c>
+      <c r="G18" t="str">
+        <v>François</v>
+      </c>
+      <c r="H18" t="str">
+        <v>franois.hollande@example.com</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J18" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>René Pleven</v>
+      <c r="A19">
+        <v>191584767</v>
+      </c>
+      <c r="B19" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="H19" t="str">
+        <v>emmanuel.macron@example.com</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J19" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>Félix Gouin</v>
+      <c r="A20">
+        <v>191584768</v>
+      </c>
+      <c r="B20" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="H20" t="str">
+        <v>emmanuel.macron@example.com</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J20" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>Paul Ramadier</v>
+      <c r="A21">
+        <v>191584769</v>
+      </c>
+      <c r="B21" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="H21" t="str">
+        <v>emmanuel.macron@example.com</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J21" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>Maurice Bourgès-Maunoury</v>
+      <c r="A22">
+        <v>191584770</v>
+      </c>
+      <c r="B22" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Macron</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Emmanuel</v>
+      </c>
+      <c r="H22" t="str">
+        <v>emmanuel.macron@example.com</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J22" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>Félix Gaillard</v>
+      <c r="A23">
+        <v>191584771</v>
+      </c>
+      <c r="B23" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Doumer</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Paul</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Doumer</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Paul</v>
+      </c>
+      <c r="H23" t="str">
+        <v>paul.doumer@example.com</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J23" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K23">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>Pierre Pflimlin</v>
+      <c r="A24">
+        <v>191584772</v>
+      </c>
+      <c r="B24" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Lebrun</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Albert</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Lebrun</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Albert</v>
+      </c>
+      <c r="H24" t="str">
+        <v>albert.lebrun@example.com</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J24" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K24">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>Michel Debré</v>
+      <c r="A25">
+        <v>191584773</v>
+      </c>
+      <c r="B25" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Lebrun</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Albert</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Lebrun</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Albert</v>
+      </c>
+      <c r="H25" t="str">
+        <v>albert.lebrun@example.com</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J25" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K25">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>Maurice Couve de Murville</v>
+      <c r="A26">
+        <v>191584774</v>
+      </c>
+      <c r="B26" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Poincaré</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Raymond</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Poincaré</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Raymond</v>
+      </c>
+      <c r="H26" t="str">
+        <v>raymond.poincar@example.com</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J26" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K26">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>Jacques Chaban-Delmas</v>
+      <c r="A27">
+        <v>191584775</v>
+      </c>
+      <c r="B27" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Fallières</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Armand</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Fallières</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Armand</v>
+      </c>
+      <c r="H27" t="str">
+        <v>armand.fallires@example.com</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J27" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K27">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>Pierre Messmer</v>
+      <c r="A28">
+        <v>191584776</v>
+      </c>
+      <c r="B28" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="H28" t="str">
+        <v>mile.loubet@example.com</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J28" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K28">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>Raymond Barre</v>
+      <c r="A29">
+        <v>191584777</v>
+      </c>
+      <c r="B29" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="H29" t="str">
+        <v>mile.loubet@example.com</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J29" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K29">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>Pierre Mauroy</v>
+      <c r="A30">
+        <v>191584778</v>
+      </c>
+      <c r="B30" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Loubet</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Émile</v>
+      </c>
+      <c r="H30" t="str">
+        <v>mile.loubet@example.com</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J30" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>Laurent Fabius</v>
+      <c r="A31">
+        <v>191584779</v>
+      </c>
+      <c r="B31" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Faure</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Félix</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Faure</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Félix</v>
+      </c>
+      <c r="H31" t="str">
+        <v>flix.faure@example.com</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J31" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K31">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>Michel Rocard</v>
+      <c r="A32">
+        <v>191584780</v>
+      </c>
+      <c r="B32" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Casimir-Perier</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Jean</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Casimir-Perier</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Jean</v>
+      </c>
+      <c r="H32" t="str">
+        <v>jean.casimirperier@example.com</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J32" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>Édith Cresson</v>
+      <c r="A33">
+        <v>191584781</v>
+      </c>
+      <c r="B33" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Carnot</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Sadi</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Carnot</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Sadi</v>
+      </c>
+      <c r="H33" t="str">
+        <v>sadi.carnot@example.com</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J33" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K33">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>Pierre Bérégovoy</v>
+      <c r="A34">
+        <v>191584782</v>
+      </c>
+      <c r="B34" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Millerand</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Alexandre</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Millerand</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Alexandre</v>
+      </c>
+      <c r="H34" t="str">
+        <v>alexandre.millerand@example.com</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J34" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K34">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>Édouard Balladur</v>
+      <c r="A35">
+        <v>191584783</v>
+      </c>
+      <c r="B35" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Millerand</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Alexandre</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Millerand</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Alexandre</v>
+      </c>
+      <c r="H35" t="str">
+        <v>alexandre.millerand@example.com</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J35" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K35">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>Alain Juppé</v>
+      <c r="A36">
+        <v>191584784</v>
+      </c>
+      <c r="B36" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Doumergue</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Gaston</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Doumergue</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Gaston</v>
+      </c>
+      <c r="H36" t="str">
+        <v>gaston.doumergue@example.com</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J36" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K36">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>Lionel Jospin</v>
+      <c r="A37">
+        <v>191584785</v>
+      </c>
+      <c r="B37" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Le Lay</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Lénaïse</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Le Lay</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Lénaïse</v>
+      </c>
+      <c r="H37" t="str">
+        <v>lnase.lelay@example.com</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J37" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K37">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>Jean-Pierre Raffarin</v>
+      <c r="A38">
+        <v>191584786</v>
+      </c>
+      <c r="B38" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Donval</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Laëtitia</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Donval</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Laëtitia</v>
+      </c>
+      <c r="H38" t="str">
+        <v>latitia.donval@example.com</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J38" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>Dominique de Villepin</v>
+      <c r="A39">
+        <v>191584787</v>
+      </c>
+      <c r="B39" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Donval</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Laëtitia</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Donval</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Laëtitia</v>
+      </c>
+      <c r="H39" t="str">
+        <v>latitia.donval@example.com</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J39" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>François Fillon</v>
+      <c r="A40">
+        <v>191584788</v>
+      </c>
+      <c r="B40" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Bouard</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Agnès</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Bouard</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Agnès</v>
+      </c>
+      <c r="H40" t="str">
+        <v>agns.bouard@example.com</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J40" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>Manuel Valls</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Bernard Cazeneuve</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Édouard Philippe</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Jean Castex</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Élisabeth Borne</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Gabriel Attal</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Simone Veil</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Georges Marchais</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Jean-Marie Le Pen</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Marine Le Pen</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Jean-Luc Mélenchon</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Ségolène Royal</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Martine Aubry</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>François Bayrou</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Philippe Séguin</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Charles Pasqua</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Jack Lang</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Robert Badinter</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Michel Barnier</v>
+      <c r="A41">
+        <v>191584789</v>
+      </c>
+      <c r="B41" t="str">
+        <v>10/09/2026 15:06</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Validé</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Pensec</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Philippe</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Pensec</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Philippe</v>
+      </c>
+      <c r="H41" t="str">
+        <v>philippe.pensec@example.com</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Carte bancaire</v>
+      </c>
+      <c r="J41" t="str">
+        <v>PRIX UNIQUE DU TICKET</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K41"/>
   </ignoredErrors>
 </worksheet>
 </file>